--- a/Junnutavling entries 2.xlsx
+++ b/Junnutavling entries 2.xlsx
@@ -10913,11 +10913,6 @@
           <t>GS U11 - 2</t>
         </is>
       </c>
-      <c r="I2" s="41" t="inlineStr">
-        <is>
-          <t>BD U17 - 1</t>
-        </is>
-      </c>
       <c r="J2" s="31" t="inlineStr">
         <is>
           <t>BS U11 - 2</t>
@@ -10933,104 +10928,89 @@
           <t>GS U11 - 3</t>
         </is>
       </c>
-      <c r="O2" s="41" t="inlineStr">
-        <is>
-          <t>BD U17 - 2</t>
-        </is>
-      </c>
-      <c r="P2" s="39" t="inlineStr">
+      <c r="P2" s="36" t="inlineStr">
+        <is>
+          <t>XD U13 - 2</t>
+        </is>
+      </c>
+      <c r="R2" s="31" t="inlineStr">
+        <is>
+          <t>BS U11 - 3</t>
+        </is>
+      </c>
+      <c r="T2" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 3</t>
+        </is>
+      </c>
+      <c r="V2" s="33" t="inlineStr">
+        <is>
+          <t>BD U11 - 3</t>
+        </is>
+      </c>
+      <c r="X2" s="36" t="inlineStr">
+        <is>
+          <t>XD U13 - 3</t>
+        </is>
+      </c>
+      <c r="Z2" s="31" t="inlineStr">
+        <is>
+          <t>BS U11 - 4</t>
+        </is>
+      </c>
+      <c r="AB2" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 3</t>
+        </is>
+      </c>
+      <c r="AD2" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 4</t>
+        </is>
+      </c>
+      <c r="AF2" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 2</t>
         </is>
       </c>
-      <c r="R2" s="31" t="inlineStr">
-        <is>
-          <t>BS U11 - 3</t>
-        </is>
-      </c>
-      <c r="T2" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 3</t>
-        </is>
-      </c>
-      <c r="V2" s="33" t="inlineStr">
-        <is>
-          <t>BD U11 - 3</t>
-        </is>
-      </c>
-      <c r="X2" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 4</t>
-        </is>
-      </c>
-      <c r="Z2" s="31" t="inlineStr">
-        <is>
-          <t>BS U11 - 4</t>
-        </is>
-      </c>
-      <c r="AB2" s="36" t="inlineStr">
-        <is>
-          <t>XD U13 - 1</t>
-        </is>
-      </c>
-      <c r="AD2" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 4</t>
-        </is>
-      </c>
-      <c r="AF2" s="39" t="inlineStr">
+      <c r="AH2" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AJ2" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 4</t>
+        </is>
+      </c>
+      <c r="AL2" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 5</t>
+        </is>
+      </c>
+      <c r="AN2" s="39" t="inlineStr">
+        <is>
+          <t>BD U13 - 3</t>
+        </is>
+      </c>
+      <c r="AP2" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 3</t>
+        </is>
+      </c>
+      <c r="AR2" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 5</t>
+        </is>
+      </c>
+      <c r="AT2" s="35" t="inlineStr">
+        <is>
+          <t>XD U17 - 3</t>
+        </is>
+      </c>
+      <c r="AV2" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 4</t>
-        </is>
-      </c>
-      <c r="AG2" s="43" t="inlineStr">
-        <is>
-          <t>GD U15 - 1</t>
-        </is>
-      </c>
-      <c r="AH2" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 4</t>
-        </is>
-      </c>
-      <c r="AJ2" s="36" t="inlineStr">
-        <is>
-          <t>XD U13 - 2</t>
-        </is>
-      </c>
-      <c r="AL2" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 5</t>
-        </is>
-      </c>
-      <c r="AM2" s="43" t="inlineStr">
-        <is>
-          <t>GD U15 - 2</t>
-        </is>
-      </c>
-      <c r="AN2" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 4</t>
-        </is>
-      </c>
-      <c r="AP2" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 4</t>
-        </is>
-      </c>
-      <c r="AR2" s="36" t="inlineStr">
-        <is>
-          <t>XD U13 - 3</t>
-        </is>
-      </c>
-      <c r="AU2" s="43" t="inlineStr">
-        <is>
-          <t>GD U15 - 3</t>
-        </is>
-      </c>
-      <c r="AV2" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 5</t>
         </is>
       </c>
     </row>
@@ -11053,9 +11033,9 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="H3" s="39" t="inlineStr">
-        <is>
-          <t>BD U13 - 1</t>
+      <c r="H3" s="36" t="inlineStr">
+        <is>
+          <t>XD U13 - 1</t>
         </is>
       </c>
       <c r="J3" s="31" t="inlineStr">
@@ -11073,94 +11053,84 @@
           <t>BD U11 - 2</t>
         </is>
       </c>
-      <c r="O3" s="41" t="inlineStr">
-        <is>
-          <t>BD U17 - 2</t>
-        </is>
-      </c>
-      <c r="P3" s="39" t="inlineStr">
+      <c r="P3" s="36" t="inlineStr">
+        <is>
+          <t>XD U13 - 2</t>
+        </is>
+      </c>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>BS U11 - 3</t>
+        </is>
+      </c>
+      <c r="T3" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 3</t>
+        </is>
+      </c>
+      <c r="V3" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 3</t>
+        </is>
+      </c>
+      <c r="X3" s="36" t="inlineStr">
+        <is>
+          <t>XD U13 - 3</t>
+        </is>
+      </c>
+      <c r="Z3" s="31" t="inlineStr">
+        <is>
+          <t>BS U11 - 4</t>
+        </is>
+      </c>
+      <c r="AB3" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 3</t>
+        </is>
+      </c>
+      <c r="AD3" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 4</t>
+        </is>
+      </c>
+      <c r="AF3" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 2</t>
         </is>
       </c>
-      <c r="R3" s="31" t="inlineStr">
-        <is>
-          <t>BS U11 - 3</t>
-        </is>
-      </c>
-      <c r="T3" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 3</t>
-        </is>
-      </c>
-      <c r="V3" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 3</t>
-        </is>
-      </c>
-      <c r="X3" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 4</t>
-        </is>
-      </c>
-      <c r="Z3" s="31" t="inlineStr">
-        <is>
-          <t>BS U11 - 4</t>
-        </is>
-      </c>
-      <c r="AB3" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 2</t>
-        </is>
-      </c>
-      <c r="AD3" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 4</t>
-        </is>
-      </c>
-      <c r="AF3" s="39" t="inlineStr">
+      <c r="AH3" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AJ3" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 4</t>
+        </is>
+      </c>
+      <c r="AN3" s="39" t="inlineStr">
+        <is>
+          <t>BD U13 - 3</t>
+        </is>
+      </c>
+      <c r="AP3" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 3</t>
+        </is>
+      </c>
+      <c r="AR3" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 5</t>
+        </is>
+      </c>
+      <c r="AT3" s="41" t="inlineStr">
+        <is>
+          <t>BD U17 - 3</t>
+        </is>
+      </c>
+      <c r="AV3" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 4</t>
-        </is>
-      </c>
-      <c r="AG3" s="43" t="inlineStr">
-        <is>
-          <t>GD U15 - 1</t>
-        </is>
-      </c>
-      <c r="AH3" s="35" t="inlineStr">
-        <is>
-          <t>GS U17 - 2</t>
-        </is>
-      </c>
-      <c r="AJ3" s="36" t="inlineStr">
-        <is>
-          <t>XD U13 - 2</t>
-        </is>
-      </c>
-      <c r="AM3" s="43" t="inlineStr">
-        <is>
-          <t>GD U15 - 2</t>
-        </is>
-      </c>
-      <c r="AN3" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 4</t>
-        </is>
-      </c>
-      <c r="AP3" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 4</t>
-        </is>
-      </c>
-      <c r="AR3" s="36" t="inlineStr">
-        <is>
-          <t>XD U13 - 3</t>
-        </is>
-      </c>
-      <c r="AV3" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 5</t>
         </is>
       </c>
     </row>
@@ -11183,9 +11153,9 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="H4" s="35" t="inlineStr">
-        <is>
-          <t>XD U17 - 1</t>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 1</t>
         </is>
       </c>
       <c r="J4" s="31" t="inlineStr">
@@ -11203,54 +11173,64 @@
           <t>BS U15 - 2</t>
         </is>
       </c>
-      <c r="P4" s="39" t="inlineStr">
+      <c r="P4" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 2</t>
+        </is>
+      </c>
+      <c r="R4" s="35" t="inlineStr">
+        <is>
+          <t>GS U17 - 2</t>
+        </is>
+      </c>
+      <c r="T4" s="39" t="inlineStr">
+        <is>
+          <t>BD U13 - 1</t>
+        </is>
+      </c>
+      <c r="V4" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 3</t>
+        </is>
+      </c>
+      <c r="Z4" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 1</t>
+        </is>
+      </c>
+      <c r="AB4" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 3</t>
+        </is>
+      </c>
+      <c r="AF4" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 2</t>
         </is>
       </c>
-      <c r="R4" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 3</t>
-        </is>
-      </c>
-      <c r="T4" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 3</t>
-        </is>
-      </c>
-      <c r="V4" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 3</t>
-        </is>
-      </c>
-      <c r="X4" s="39" t="inlineStr">
-        <is>
-          <t>BD U13 - 3</t>
-        </is>
-      </c>
-      <c r="Z4" s="40" t="inlineStr">
-        <is>
-          <t>GS U15 - 4</t>
-        </is>
-      </c>
-      <c r="AB4" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 2</t>
-        </is>
-      </c>
-      <c r="AJ4" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 3</t>
+      <c r="AH4" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AJ4" s="43" t="inlineStr">
+        <is>
+          <t>GD U15 - 1</t>
         </is>
       </c>
       <c r="AN4" s="35" t="inlineStr">
         <is>
-          <t>GS U17 - 3</t>
-        </is>
-      </c>
-      <c r="AV4" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 5</t>
+          <t>XD U17 - 2</t>
+        </is>
+      </c>
+      <c r="AP4" s="43" t="inlineStr">
+        <is>
+          <t>GD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AV4" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 4</t>
         </is>
       </c>
     </row>
@@ -11273,6 +11253,11 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
+      <c r="H5" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 1</t>
+        </is>
+      </c>
       <c r="J5" s="31" t="inlineStr">
         <is>
           <t>BS U11 - 2</t>
@@ -11288,44 +11273,54 @@
           <t>BS U15 - 2</t>
         </is>
       </c>
-      <c r="P5" s="39" t="inlineStr">
+      <c r="P5" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 2</t>
+        </is>
+      </c>
+      <c r="V5" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 3</t>
+        </is>
+      </c>
+      <c r="Z5" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 1</t>
+        </is>
+      </c>
+      <c r="AB5" s="32" t="inlineStr">
+        <is>
+          <t>BS U13 - 3</t>
+        </is>
+      </c>
+      <c r="AF5" s="39" t="inlineStr">
         <is>
           <t>BD U13 - 2</t>
         </is>
       </c>
-      <c r="R5" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 3</t>
-        </is>
-      </c>
-      <c r="T5" s="32" t="inlineStr">
-        <is>
-          <t>BS U13 - 3</t>
-        </is>
-      </c>
-      <c r="V5" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 3</t>
-        </is>
-      </c>
-      <c r="X5" s="39" t="inlineStr">
-        <is>
-          <t>BD U13 - 3</t>
-        </is>
-      </c>
-      <c r="Z5" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 3</t>
-        </is>
-      </c>
-      <c r="AB5" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 2</t>
-        </is>
-      </c>
-      <c r="AJ5" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 3</t>
+      <c r="AH5" s="40" t="inlineStr">
+        <is>
+          <t>BD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AJ5" s="43" t="inlineStr">
+        <is>
+          <t>GD U15 - 1</t>
+        </is>
+      </c>
+      <c r="AN5" s="41" t="inlineStr">
+        <is>
+          <t>BD U17 - 2</t>
+        </is>
+      </c>
+      <c r="AP5" s="43" t="inlineStr">
+        <is>
+          <t>GD U15 - 2</t>
+        </is>
+      </c>
+      <c r="AV5" s="43" t="inlineStr">
+        <is>
+          <t>GD U15 - 3</t>
         </is>
       </c>
     </row>
@@ -11348,9 +11343,9 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 2</t>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 1</t>
         </is>
       </c>
       <c r="L6" s="32" t="inlineStr">
@@ -11363,19 +11358,9 @@
           <t>BS U15 - 2</t>
         </is>
       </c>
-      <c r="P6" s="35" t="inlineStr">
-        <is>
-          <t>XD U17 - 2</t>
-        </is>
-      </c>
-      <c r="R6" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 2</t>
-        </is>
-      </c>
-      <c r="T6" s="40" t="inlineStr">
-        <is>
-          <t>GS U15 - 3</t>
+      <c r="P6" s="38" t="inlineStr">
+        <is>
+          <t>BS U15 - 2</t>
         </is>
       </c>
       <c r="V6" s="38" t="inlineStr">
@@ -11383,24 +11368,29 @@
           <t>BS U15 - 3</t>
         </is>
       </c>
-      <c r="X6" s="35" t="inlineStr">
-        <is>
-          <t>XD U17 - 3</t>
-        </is>
-      </c>
-      <c r="Z6" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 3</t>
-        </is>
-      </c>
-      <c r="AB6" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 2</t>
+      <c r="Z6" s="35" t="inlineStr">
+        <is>
+          <t>GS U17 - 3</t>
+        </is>
+      </c>
+      <c r="AB6" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 4</t>
+        </is>
+      </c>
+      <c r="AF6" s="35" t="inlineStr">
+        <is>
+          <t>XD U17 - 1</t>
         </is>
       </c>
       <c r="AJ6" s="42" t="inlineStr">
         <is>
-          <t>BS U17 - 3</t>
+          <t>BS U17 - 5</t>
+        </is>
+      </c>
+      <c r="AN6" s="41" t="inlineStr">
+        <is>
+          <t>BD U17 - 2</t>
         </is>
       </c>
     </row>
@@ -11423,9 +11413,9 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="J7" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 2</t>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>GS U17 - 1</t>
         </is>
       </c>
       <c r="L7" s="32" t="inlineStr">
@@ -11438,29 +11428,24 @@
           <t>BS U15 - 2</t>
         </is>
       </c>
-      <c r="R7" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 2</t>
-        </is>
-      </c>
-      <c r="T7" s="40" t="inlineStr">
+      <c r="P7" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V7" s="40" t="inlineStr">
         <is>
           <t>GS U15 - 3</t>
         </is>
       </c>
-      <c r="X7" s="41" t="inlineStr">
-        <is>
-          <t>BD U17 - 3</t>
-        </is>
-      </c>
-      <c r="AB7" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 2</t>
-        </is>
-      </c>
-      <c r="AJ7" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 3</t>
+      <c r="AB7" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 4</t>
+        </is>
+      </c>
+      <c r="AF7" s="41" t="inlineStr">
+        <is>
+          <t>BD U17 - 1</t>
         </is>
       </c>
     </row>
@@ -11483,11 +11468,6 @@
           <t>GS U15 - 1</t>
         </is>
       </c>
-      <c r="J8" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 2</t>
-        </is>
-      </c>
       <c r="L8" s="32" t="inlineStr">
         <is>
           <t>BS U13 - 2</t>
@@ -11498,19 +11478,19 @@
           <t>BS U15 - 2</t>
         </is>
       </c>
-      <c r="R8" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 2</t>
-        </is>
-      </c>
-      <c r="T8" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 1</t>
-        </is>
-      </c>
-      <c r="AB8" s="42" t="inlineStr">
+      <c r="P8" s="42" t="inlineStr">
         <is>
           <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V8" s="40" t="inlineStr">
+        <is>
+          <t>GS U15 - 3</t>
+        </is>
+      </c>
+      <c r="AB8" s="40" t="inlineStr">
+        <is>
+          <t>GS U15 - 4</t>
         </is>
       </c>
     </row>
@@ -11533,34 +11513,29 @@
           <t>GS U15 - 1</t>
         </is>
       </c>
-      <c r="J9" s="37" t="inlineStr">
-        <is>
-          <t>GS U13 - 2</t>
-        </is>
-      </c>
       <c r="L9" s="32" t="inlineStr">
         <is>
           <t>BS U13 - 2</t>
         </is>
       </c>
-      <c r="N9" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 2</t>
-        </is>
-      </c>
-      <c r="R9" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 2</t>
-        </is>
-      </c>
-      <c r="T9" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 1</t>
+      <c r="N9" s="40" t="inlineStr">
+        <is>
+          <t>GS U15 - 2</t>
+        </is>
+      </c>
+      <c r="P9" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V9" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 3</t>
         </is>
       </c>
       <c r="AB9" s="42" t="inlineStr">
         <is>
-          <t>BS U17 - 2</t>
+          <t>BS U17 - 4</t>
         </is>
       </c>
     </row>
@@ -11583,29 +11558,29 @@
           <t>GS U15 - 1</t>
         </is>
       </c>
-      <c r="J10" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 1</t>
-        </is>
-      </c>
-      <c r="L10" s="40" t="inlineStr">
+      <c r="L10" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 2</t>
+        </is>
+      </c>
+      <c r="N10" s="40" t="inlineStr">
         <is>
           <t>GS U15 - 2</t>
         </is>
       </c>
-      <c r="N10" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 2</t>
-        </is>
-      </c>
-      <c r="T10" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 1</t>
+      <c r="P10" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V10" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 3</t>
         </is>
       </c>
       <c r="AB10" s="42" t="inlineStr">
         <is>
-          <t>BS U17 - 2</t>
+          <t>BS U17 - 4</t>
         </is>
       </c>
     </row>
@@ -11623,29 +11598,29 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="J11" s="40" t="inlineStr">
-        <is>
-          <t>BD U15 - 1</t>
-        </is>
-      </c>
-      <c r="L11" s="40" t="inlineStr">
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 1</t>
+        </is>
+      </c>
+      <c r="L11" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 2</t>
+        </is>
+      </c>
+      <c r="N11" s="40" t="inlineStr">
         <is>
           <t>GS U15 - 2</t>
         </is>
       </c>
-      <c r="N11" s="38" t="inlineStr">
-        <is>
-          <t>BS U15 - 2</t>
-        </is>
-      </c>
-      <c r="T11" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 1</t>
-        </is>
-      </c>
-      <c r="AB11" s="35" t="inlineStr">
-        <is>
-          <t>GS U17 - 1</t>
+      <c r="P11" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V11" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 3</t>
         </is>
       </c>
     </row>
@@ -11663,14 +11638,29 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="L12" s="40" t="inlineStr">
+      <c r="F12" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 1</t>
+        </is>
+      </c>
+      <c r="L12" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 2</t>
+        </is>
+      </c>
+      <c r="N12" s="40" t="inlineStr">
         <is>
           <t>GS U15 - 2</t>
         </is>
       </c>
-      <c r="T12" s="42" t="inlineStr">
-        <is>
-          <t>BS U17 - 1</t>
+      <c r="P12" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="V12" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 3</t>
         </is>
       </c>
     </row>
@@ -11688,14 +11678,24 @@
           <t>BS U15 - 1</t>
         </is>
       </c>
-      <c r="L13" s="40" t="inlineStr">
-        <is>
-          <t>GS U15 - 2</t>
-        </is>
-      </c>
-      <c r="T13" s="42" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>BS U17 - 1</t>
+        </is>
+      </c>
+      <c r="L13" s="37" t="inlineStr">
+        <is>
+          <t>GS U13 - 2</t>
+        </is>
+      </c>
+      <c r="N13" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
+        </is>
+      </c>
+      <c r="P13" s="42" t="inlineStr">
+        <is>
+          <t>BS U17 - 2</t>
         </is>
       </c>
     </row>
